--- a/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2019_T4_0.xlsx
+++ b/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2019_T4_0.xlsx
@@ -45,7 +45,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>79</t>
+    <t>73</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -57,40 +57,40 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>0.304</t>
-  </si>
-  <si>
-    <t>(0.052)</t>
-  </si>
-  <si>
-    <t>0.456</t>
-  </si>
-  <si>
-    <t>(0.056)</t>
-  </si>
-  <si>
-    <t>0.253</t>
-  </si>
-  <si>
-    <t>(0.049)</t>
-  </si>
-  <si>
-    <t>0.987</t>
-  </si>
-  <si>
-    <t>(0.317)</t>
-  </si>
-  <si>
-    <t>1.114</t>
-  </si>
-  <si>
-    <t>(0.187)</t>
-  </si>
-  <si>
-    <t>0.392</t>
-  </si>
-  <si>
-    <t>(0.091)</t>
+    <t>0.329</t>
+  </si>
+  <si>
+    <t>(0.055)</t>
+  </si>
+  <si>
+    <t>0.493</t>
+  </si>
+  <si>
+    <t>(0.059)</t>
+  </si>
+  <si>
+    <t>0.274</t>
+  </si>
+  <si>
+    <t>(0.053)</t>
+  </si>
+  <si>
+    <t>1.068</t>
+  </si>
+  <si>
+    <t>(0.342)</t>
+  </si>
+  <si>
+    <t>1.205</t>
+  </si>
+  <si>
+    <t>(0.199)</t>
+  </si>
+  <si>
+    <t>0.425</t>
+  </si>
+  <si>
+    <t>(0.097)</t>
   </si>
   <si>
     <t>37</t>
@@ -138,7 +138,7 @@
     <t>(0.259)</t>
   </si>
   <si>
-    <t>116</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -150,22 +150,22 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.237**</t>
-  </si>
-  <si>
-    <t>0.355***</t>
-  </si>
-  <si>
-    <t>0.423***</t>
-  </si>
-  <si>
-    <t>1.175</t>
-  </si>
-  <si>
-    <t>2.264***</t>
-  </si>
-  <si>
-    <t>1.121***</t>
+    <t>0.212**</t>
+  </si>
+  <si>
+    <t>0.318***</t>
+  </si>
+  <si>
+    <t>0.402***</t>
+  </si>
+  <si>
+    <t>1.094</t>
+  </si>
+  <si>
+    <t>2.173***</t>
+  </si>
+  <si>
+    <t>1.089***</t>
   </si>
 </sst>
 </file>
